--- a/data/Classes_2026_biotech.xlsx
+++ b/data/Classes_2026_biotech.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9264"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="81">
   <si>
     <t>Family</t>
   </si>
@@ -246,6 +246,30 @@
   </si>
   <si>
     <t>st142999@student.spbu.ru</t>
+  </si>
+  <si>
+    <t>Андриеш</t>
+  </si>
+  <si>
+    <t>Ангелина</t>
+  </si>
+  <si>
+    <t>Валерьевна</t>
+  </si>
+  <si>
+    <t>st150414</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Краснова</t>
+  </si>
+  <si>
+    <t>Олеговна</t>
+  </si>
+  <si>
+    <t>st097958</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="4" max="4" width="9.11111111111111" customWidth="1"/>
@@ -1666,6 +1690,40 @@
         <v>72</v>
       </c>
     </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="st142856"/>
